--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationquantity.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationquantity.xlsx
@@ -266,7 +266,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
   </si>
   <si>
@@ -331,7 +331,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -357,7 +357,7 @@
     <t>精度は、測定のほとんどすべての場合に暗黙的に処理されます。 / Precision is handled implicitly in almost all cases of measurement.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
